--- a/artfynd/A 8917-2024 artfynd.xlsx
+++ b/artfynd/A 8917-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130673667</v>
       </c>
       <c r="B2" t="n">
-        <v>57846</v>
+        <v>57848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8917-2024 artfynd.xlsx
+++ b/artfynd/A 8917-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130673667</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8917-2024 artfynd.xlsx
+++ b/artfynd/A 8917-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130673667</v>
       </c>
       <c r="B2" t="n">
-        <v>57856</v>
+        <v>57857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8917-2024 artfynd.xlsx
+++ b/artfynd/A 8917-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130673667</v>
       </c>
       <c r="B2" t="n">
-        <v>57857</v>
+        <v>57858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8917-2024 artfynd.xlsx
+++ b/artfynd/A 8917-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130673667</v>
+        <v>97767374</v>
       </c>
       <c r="B2" t="n">
-        <v>57878</v>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Löpsjötorp, Srm</t>
+          <t>Harpebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573636</v>
+        <v>573663</v>
       </c>
       <c r="R2" t="n">
-        <v>6525683</v>
+        <v>6525657</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>1981-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>1981-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,19 +756,340 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130673667</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Löpsjötorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>573636</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6525683</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Samuel Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130673666</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Löpsjötorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573644</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6525684</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4956386</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Harpebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573638</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6525735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-11-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-11-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lövdunge i vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8917-2024 artfynd.xlsx
+++ b/artfynd/A 8917-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97767374</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130673667</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130673666</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,8 +1110,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4956386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>